--- a/pipeline_output/Madhyapradesh_2W_H&M.xlsx
+++ b/pipeline_output/Madhyapradesh_2W_H&M.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7063,12 +7063,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10399,12 +10399,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -10750,12 +10750,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -11101,12 +11101,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -11218,12 +11218,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12886,12 +12886,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -13598,12 +13598,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -14223,12 +14223,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -14574,12 +14574,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15199,12 +15199,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -15443,12 +15443,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -15570,12 +15570,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -15687,12 +15687,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -15941,12 +15941,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -16058,12 +16058,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -16185,12 +16185,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, HARYANA, MADHYA PRADESH, WEST BENGAL</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -16312,12 +16312,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16429,12 +16429,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16556,12 +16556,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16683,12 +16683,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -16937,12 +16937,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17054,12 +17054,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17171,12 +17171,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17288,12 +17288,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17405,12 +17405,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17522,12 +17522,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17649,12 +17649,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17776,12 +17776,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -17903,12 +17903,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18030,12 +18030,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18274,12 +18274,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18401,12 +18401,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18518,12 +18518,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18645,12 +18645,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18772,12 +18772,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18889,12 +18889,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19016,12 +19016,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19143,12 +19143,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -19387,12 +19387,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -19514,12 +19514,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -19641,12 +19641,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -19768,12 +19768,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -19885,12 +19885,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -20002,12 +20002,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20181,7 +20181,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -20236,12 +20236,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -20353,12 +20353,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20415,7 +20415,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -20480,12 +20480,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -20607,12 +20607,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -20734,12 +20734,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20796,7 +20796,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -20861,12 +20861,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -21105,12 +21105,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -21232,12 +21232,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -21349,12 +21349,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -21476,12 +21476,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -21603,12 +21603,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -21720,12 +21720,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21782,7 +21782,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -21847,12 +21847,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>CHHATTISGARH</t>
+          <t>CHHATTISGARH, MADHYA PRADESH</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -21974,12 +21974,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22091,12 +22091,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22345,12 +22345,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22472,12 +22472,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22599,12 +22599,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22716,12 +22716,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22833,12 +22833,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -22950,12 +22950,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23067,12 +23067,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23184,12 +23184,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23311,12 +23311,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23438,12 +23438,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -23565,12 +23565,12 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -23692,12 +23692,12 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -23936,12 +23936,12 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -24063,12 +24063,12 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -24180,12 +24180,12 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -24307,12 +24307,12 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -24434,12 +24434,12 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -24551,12 +24551,12 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -24678,12 +24678,12 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -24805,12 +24805,12 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -24932,12 +24932,12 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -25059,12 +25059,12 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -25186,12 +25186,12 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -25313,12 +25313,12 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -25440,12 +25440,12 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -25567,12 +25567,12 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -25694,12 +25694,12 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -25821,12 +25821,12 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -25938,12 +25938,12 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -26055,12 +26055,12 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -26172,12 +26172,12 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -26289,12 +26289,12 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -26406,12 +26406,12 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -26523,12 +26523,12 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -26640,12 +26640,12 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -26757,12 +26757,12 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -26991,12 +26991,12 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -27108,12 +27108,12 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -27225,12 +27225,12 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -27342,12 +27342,12 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -27459,12 +27459,12 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -27693,12 +27693,12 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -27820,12 +27820,12 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -27947,12 +27947,12 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -28201,12 +28201,12 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -28328,12 +28328,12 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -28455,12 +28455,12 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -28582,12 +28582,12 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -28709,12 +28709,12 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -28826,12 +28826,12 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -28943,12 +28943,12 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -29060,12 +29060,12 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -29177,12 +29177,12 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -29294,12 +29294,12 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -29411,12 +29411,12 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -29528,12 +29528,12 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
@@ -29645,12 +29645,12 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -29762,12 +29762,12 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -29879,12 +29879,12 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -29996,12 +29996,12 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN242" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -30113,12 +30113,12 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -30230,12 +30230,12 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -30347,12 +30347,12 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN245" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
@@ -30464,12 +30464,12 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
@@ -30581,12 +30581,12 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
